--- a/artfynd/A 46706-2025 artfynd.xlsx
+++ b/artfynd/A 46706-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74857339</v>
       </c>
       <c r="B2" t="n">
-        <v>105642</v>
+        <v>105651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46706-2025 artfynd.xlsx
+++ b/artfynd/A 46706-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74857339</v>
       </c>
       <c r="B2" t="n">
-        <v>105651</v>
+        <v>105654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46706-2025 artfynd.xlsx
+++ b/artfynd/A 46706-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74857339</v>
       </c>
       <c r="B2" t="n">
-        <v>105654</v>
+        <v>105682</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46706-2025 artfynd.xlsx
+++ b/artfynd/A 46706-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74857339</v>
       </c>
       <c r="B2" t="n">
-        <v>105682</v>
+        <v>105688</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46706-2025 artfynd.xlsx
+++ b/artfynd/A 46706-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74857339</v>
       </c>
       <c r="B2" t="n">
-        <v>105688</v>
+        <v>105695</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46706-2025 artfynd.xlsx
+++ b/artfynd/A 46706-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74857339</v>
       </c>
       <c r="B2" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46706-2025 artfynd.xlsx
+++ b/artfynd/A 46706-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74857339</v>
       </c>
       <c r="B2" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46706-2025 artfynd.xlsx
+++ b/artfynd/A 46706-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74857339</v>
       </c>
       <c r="B2" t="n">
-        <v>105709</v>
+        <v>105714</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46706-2025 artfynd.xlsx
+++ b/artfynd/A 46706-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74857339</v>
       </c>
       <c r="B2" t="n">
-        <v>105714</v>
+        <v>105722</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46706-2025 artfynd.xlsx
+++ b/artfynd/A 46706-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74857339</v>
       </c>
       <c r="B2" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46706-2025 artfynd.xlsx
+++ b/artfynd/A 46706-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74857339</v>
       </c>
       <c r="B2" t="n">
-        <v>105732</v>
+        <v>106243</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
